--- a/xpressbees_rankings_jun-sep_2026.xlsx
+++ b/xpressbees_rankings_jun-sep_2026.xlsx
@@ -76,14 +76,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,8 +461,8 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -469,7 +478,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ranking page</t>
+          <t>Ranking page URL</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -499,703 +508,706 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>B2C Logistics Service</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2.1 (P1)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>3.4 (P1)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>B2B Logistics Services</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2.4 (P1)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2.6 (P1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2.7 (P1)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2.4 (P1)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ecommerce delivery</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>6.6 (P1)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>5.6 (P1)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>5.5 (P1)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3.6 (P1)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>courier service</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>16.9 (P2)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>14.9 (P2)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>11.1 (P2)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>12.7 (P2)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>logistics transportation services</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>/blog/logistics-transportation-service/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/logistics-transportation-service/</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>9.7 (P1)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>22.9 (P3)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>57.5 (P6)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>24.3 (P3)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>logistics service provider</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>/ / /blog/logistics-service-provider/</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Jun: https://www.xpressbees.com/blog/logistics-service-provider/
+Jul: https://www.xpressbees.com/
+Aug: https://www.xpressbees.com/
+Sep: https://www.xpressbees.com/blog/logistics-service-provider/</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>4.1 (P1)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>6.0 (P1)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>4.7 (P1)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>6.7 (P1)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>cheap courier service</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>/blog/cheap-courier-services-for-businesses/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/cheap-courier-services-for-businesses/</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>9.6 (P1)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>13.9 (P2)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>9.2 (P1)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>14.4 (P2)</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>fast courier service</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>9.5 (P1)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>10.0 (P1)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>10.3 (P2)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>11.3 (P2)</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ecommerce delivery service</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>11.8 (P2)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>11.0 (P2)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>9.8 (P1)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>3.8 (P1)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>international courier services</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>12.8 (P2)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>19.1 (P2)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>29.3 (P3)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>31.9 (P4)</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>logistics company</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>7.0 (P1)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>6.9 (P1)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>4.5 (P1)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>6.0 (P1)</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>international shipping</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>/blog/what-is-international-shipping/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-international-shipping/</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>7.5 (P1)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>7.2 (P1)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>6.9 (P1)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>7.5 (P1)</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>warehouse logistics</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>/blog/what-is-warehouse-logistics/</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-warehouse-logistics/</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>5.5 (P1)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>5.8 (P1)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>6.4 (P1)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>6.2 (P1)</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>3pl logistics (service page)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>/services/third-party-logistics</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/third-party-logistics</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>8.5 (P1)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>15.1 (P2)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>11.9 (P2)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>10.7 (P2)</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>warehousing</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>/blog/what-is-warehousing/</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-warehousing/</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>11.1 (P2)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>10.6 (P2)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>11.2 (P2)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>9.9 (P1)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>last mile delivery services</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>/blog/what-is-last-mile-delivery/</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-last-mile-delivery/</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>5.7 (P1)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>6.4 (P1)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>6.4 (P1)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>7.6 (P1)</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>fulfillment center (service page)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>/services/third-party-logistics/fulfillment-center</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/third-party-logistics/fulfillment-center</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>4.2 (P1)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>12.6 (P2)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>23.9 (P3)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>18.6 (P2)</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>full truck load logistics</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/full-truck-load</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/full-truck-load</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>8.2 (P1)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>1.3 (P1)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2.1 (P1)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>3.6 (P1)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Part Truck Load (service page)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/part-truck-load</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/part-truck-load</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>17.5 (P2)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>23.9 (P3)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>19.4 (P2)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>12.6 (P2)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -1215,8 +1227,8 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -1232,7 +1244,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ranking page</t>
+          <t>Ranking page URL</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1262,814 +1274,815 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>line haul transport</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/line-haul-hub-to-hub-movement</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/line-haul-hub-to-hub-movement</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>5 (P1)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>7.2 (P1)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>7 (P1)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>6 (P1)</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>D2C Logistics</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/d2c-logistics</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/d2c-logistics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>1.3 (P1)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>1.4 (P1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1.2 (P1)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1.4 (P1)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>E-commerce Logistics Solutions</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/e-commerce-logistics</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/e-commerce-logistics</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>4 (P1)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>16 (P2)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>11.3 (P2)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Express Parcel Delivery</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>5.7 (P1)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>7.7 (P1)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>8.5 (P1)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>9.8 (P1)</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Micro-Fulfillment Services</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/micro-fulfillment-warehousing</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/micro-fulfillment-warehousing</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>6 (P1)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>5.1 (P1)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>COD Digital Payment Options</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/cod-digital-payment-options</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/cod-digital-payment-options</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2.5 (P1)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1.8 (P1)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Quick Commerce Delivery</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/quick-commerce-delivery</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/quick-commerce-delivery</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2.9 (P1)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2.5 (P1)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2.4 (P1)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>3.4 (P1)</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Quick Commerce Delivery Services</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/quick-commerce-delivery</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/quick-commerce-delivery</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>3 (P1)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>6.9 (P1)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Omnichannel Logistics</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/omnichannel-logistics</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/omnichannel-logistics</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>8.9 (P1)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>7 (P1)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>7 (P1)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>b2c Reverse Logistics</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>/ / /services/b2c-logistics-services</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Aug: https://www.xpressbees.com/
+Sep: https://www.xpressbees.com/services/b2c-logistics-services</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>65 (P7)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>15.7 (P2)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Last Mile Delivery (service page)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>/services/b2c-logistics-services/last-mile-delivery</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2c-logistics-services/last-mile-delivery</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>6.6 (P1)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>5 (P1)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>7 (P1)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>LOST</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Partial Truck Load service</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/part-truck-load</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/part-truck-load</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>5 (P1)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Full Truck Load Solutions</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/full-truck-load</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/full-truck-load</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1.9 (P1)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>3.3 (P1)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Warehouse Distribution Logistics</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/warehouse-distribution-logistics</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/warehouse-distribution-logistics</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>5 (P1)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>4 (P1)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2.3 (P1)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2 (P1)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>SME MSME Logistics</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/sme-msme-logistics-solutions</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/sme-msme-logistics-solutions</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>3.2 (P1)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1 (P1)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Hyperlocal B2B &amp; Retail</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/hyperlocal-b2b-retail-logistics</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/hyperlocal-b2b-retail-logistics</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1.9 (P1)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1.8 (P1)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Less Than Truckload</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>/blog/less-than-truckload-shipping/</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/less-than-truckload-shipping/</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>7.7 (P1)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>8.7 (P1)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>8.4 (P1)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>6.4 (P1)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>B2B Reverse Logistics</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>/services/b2b-logistics-services/reverse-logistics-rto-handling</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/b2b-logistics-services/reverse-logistics-rto-handling</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>6 (P1)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>10.2 (P2)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Express Shipment</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>/shipment/tracking</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/shipment/tracking</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>2.0 (P1)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2.0 (P1)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1.9 (P1)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2.0 (P1)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Last-Mile International</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>/services/international-courier-services/last-mile-international-delivery-solutions</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/international-courier-services/last-mile-international-delivery-solutions</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1 (P1)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1 (P1)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Cross Border eCommerce</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>/services/international-courier-services/cross-border-e-commerce-solutions</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/international-courier-services/cross-border-e-commerce-solutions</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>32 (P4)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>24.5 (P3)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Dark warehousing</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>/services/third-party-logistics/dark-warehousing</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/third-party-logistics/dark-warehousing</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>6.8 (P1)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>7.4 (P1)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>9.3 (P1)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>9.9 (P1)</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
@@ -2089,8 +2102,8 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -2106,7 +2119,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ranking page</t>
+          <t>Ranking page URL</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2136,1073 +2149,1073 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cheap courier services</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>/blog/cheap-courier-services-for-businesses/</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/cheap-courier-services-for-businesses/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>9.6 (P1)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>13.9 (P2)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>9.2 (P1)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>14.4 (P2)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Hyperlocal delivery</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>/blog/hyperlocal-delivery/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/hyperlocal-delivery/</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>4.5 (P1)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>5.3 (P1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>5.8 (P1)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>5.9 (P1)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>E-commerce delivery</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>/blog/e-commerce-delivery-solutions/</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/e-commerce-delivery-solutions/</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>6.3 (P1)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>6 (P1)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>5.2 (P1)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>5.2 (P1)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>third party logistics services</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>/blog/what-is-3pl/</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-3pl/</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>7.7 (P1)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>4.4 (P1)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>4.6 (P1)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>4.8 (P1)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Fast courier service</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>/blog/fast-courier-service/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/fast-courier-service/</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>6.1 (P1)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>7.2 (P1)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>9.8 (P1)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>9.6 (P1)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Ecommerce logistics</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>/blog/what-is-ecommerce-logistics/</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-ecommerce-logistics/</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>3.8 (P1)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>4.1 (P1)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>4.9 (P1)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>4.9 (P1)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>fulfillment centre</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>/blog/what-is-a-fulfillment-centre/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-a-fulfillment-centre/</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>3.7 (P1)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2.7 (P1)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>4.2 (P1)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>3.6 (P1)</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>fulfillment center (blog)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>/blog/what-is-a-fulfillment-centre/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-a-fulfillment-centre/</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>5.9 (P1)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>5.1 (P1)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>4.7 (P1)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>3.6 (P1)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>logistics service provider</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>/blog/logistics-service-provider/</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/logistics-service-provider/</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>4.1 (P1)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>5.8 (P1)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>9.4 (P1)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>6.7 (P1)</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Part truck load</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>/blog/part-truck-load-for-emerging-businesses/</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/part-truck-load-for-emerging-businesses/</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>3.9 (P1)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>5.7 (P1)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>5.9 (P1)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>6.3 (P1)</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>International Freight Shipping</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>/blog/international-freight-shipping/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/international-freight-shipping/</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>5.7 (P1)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>5.8 (P1)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>5.7 (P1)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>6.2 (P1)</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Full truckload</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>/blog/full-truckload-shipping/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/full-truckload-shipping/</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>3.3 (P1)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>5 (P1)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>6.1 (P1)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>4.8 (P1)</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>last mile delivery</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>/blog/what-is-last-mile-delivery/</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-last-mile-delivery/</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>9.8 (P1)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>7.5 (P1)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>7.3 (P1)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>8.2 (P1)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ecommerce delivery</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>/blog/ecommerce-delivery/</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/ecommerce-delivery/</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>11.4 (P2)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>27.2 (P3)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>8 (P1)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Fast courier (why-matters)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>/blog/why-fast-courier-service-matters/</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/why-fast-courier-service-matters/</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>3 (P1)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>14 (P2)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>17 (P2)</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>warehouse logistics</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>/blog/what-is-warehouse-logistics/</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-warehouse-logistics/</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>5.5 (P1)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>5.8 (P1)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>6.4 (P1)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>6.2 (P1)</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>e commerce supply chain</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>/blog/e-commerce-supply-chain/</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/e-commerce-supply-chain/</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>4.7 (P1)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>7.6 (P1)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>8.7 (P1)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>in-house logistics</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>/blog/3pl-vs-in-house-logistics/</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/3pl-vs-in-house-logistics/</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>9.4 (P1)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>11 (P2)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>10 (P1)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>9.7 (P1)</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>shopify shipping solutions</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>/blog/shopify-shipping-solutions/</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/shopify-shipping-solutions/</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>8.3 (P1)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>10.4 (P2)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>7.8 (P1)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>E-commerce supply chain (vs traditional)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>/blog/e-commerce-supply-chain-vs-traditional/</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/e-commerce-supply-chain-vs-traditional/</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>11 (P2)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>7 (P1)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>3PL logistics</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>/blog/what-is-3pl/</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-3pl/</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>8.8 (P1)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>9.0 (P1)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>10.7 (P2)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>9.1 (P1)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>3PL logistics (b2b blog)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>/blog/3pl-logistics-b2b-ecommerce-supply-chains/</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/3pl-logistics-b2b-ecommerce-supply-chains/</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>8.7 (P1)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>9 (P1)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>12.2 (P2)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>LOST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>less than truckload</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>/blog/less-than-truckload-shipping/</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/less-than-truckload-shipping/</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>7.7 (P1)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>8.7 (P1)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>8.4 (P1)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>6.4 (P1)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>quick commerce delivery</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>/blog/quick-commerce/</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/quick-commerce/</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>14.7 (P2)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>12 (P2)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>14.2 (P2)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>7.8 (P1)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>international shipping</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>/blog/what-is-international-shipping/</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-international-shipping/</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>7.5 (P1)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>7.2 (P1)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>6.9 (P1)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>7.5 (P1)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>warehousing</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>/blog/what-is-warehousing/</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/what-is-warehousing/</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>11.1 (P2)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>10.6 (P2)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>11.2 (P2)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>9.9 (P1)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>B2B courier services</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>/blog/b2b-courier-services/</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/b2b-courier-services/</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>6.0 (P1)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>6.1 (P1)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>7.5 (P1)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>6.9 (P1)</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>3PL logistics solutions</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>/blog/3pl-logistics-solutions/</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/3pl-logistics-solutions/</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>1 (P1)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>1 (P1)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1 (P1)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1.8 (P1)</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Logistics transportation service</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>/blog/logistics-transportation-service/</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/blog/logistics-transportation-service/</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>11.3 (P2)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>7 (P1)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>6.2 (P1)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>3.2 (P1)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>▲</t>
         </is>
@@ -3219,713 +3232,844 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>City page URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>June</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Home 13</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Home 13</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>courier services in bangalore</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-banglore</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>13.1 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>13.1 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>41.5 (P5)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>38.5 (P4)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>courier services in kolkata</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-kolkata</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>24.7 (P3)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>25.8 (P3)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>23.1 (P3)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>19.3 (P2)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Home 20</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Home 23</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Home 26</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Home 20</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>courier services in delhi</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-delhi</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>19.8 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23.0 (P3) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26.4 (P3) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20.5 (P3) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Home 11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Home 17</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Home 31</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Home 11</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>courier services in mumbai</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-mumbai</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10.7 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17.2 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31.0 (P4) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11.3 (P2) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Home 10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>courier services in hyderabad</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-hyderabad</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10.2 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>49.0 (P5)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Home 10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Home 10</t>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10.2 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9.5 (P1) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gurgaon</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Home 36</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Broken URL 2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Home 36</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>courier services in gurgaon</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-gurgaon</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>36.0 (P4) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2.0 (P1) – https://www.xpressbees.com/blog/cheap-courier-services-for-businesses/</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36.0 (P4) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Home 11</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Home 12</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Home 9</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Home 10</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>courier services in pune</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-pune</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11.3 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11.8 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9.4 (P1) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10.3 (P2) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Indore</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Broken URL 1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Broken URL 6</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Broken URL 56</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Broken URL 8</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>courier services in indore</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-indore</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1.0 (P1) – https://www.xpressbees.com/,%20https://www.delhivery.com/,%20https://dtdc.in/</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5.7 (P1) – https://www.xpressbees.com/,%20https://www.delhivery.com/,%20https://dtdc.in/</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56.2 (P6) – https://www.xpressbees.com/,%20https://www.delhivery.com/,%20https://dtdc.in/</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7.7 (P1) – https://www.xpressbees.com/,%20https://www.delhivery.com/,%20https://dtdc.in/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bhubaneswar</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>courier services in bhubaneswar</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-bhubaneswar</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>23.7 (P3)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>20.0 (P2)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>20.0 (P2)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>17.2 (P2)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chandigarh</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Home 25</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>courier services in chandigarh</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-chandigarh</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>25.0 (P3) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>24.0 (P3)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ahmedabad</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Home 9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Home 10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>courier services in ahmedabad</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-ahmedabad</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9.4 (P1) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10.4 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>38.0 (P4)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>41.3 (P5)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Home 16</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Home 20</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>courier services in noida</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-noida</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>16.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19.5 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>20.7 (P3)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>18.5 (P2)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jaipur</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Home 17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>courier services in jaipur</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-jaipur</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>17.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>38.7 (P4)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>72.0 (P8)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Home 18</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17.5 (P2) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vadodara</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>courier services in vadodara</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-vadodara</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Patna</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>courier services in patna</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-patna</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>20.0 (P2)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>19.6 (P2)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>22.0 (P3)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>17.1 (P2)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ludhiana</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Home 20</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Home 16</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Home 12</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>courier services in ludhiana</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-ludhiana</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15.5 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>22.0 (P3)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Bhopal</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Home 12</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>courier services in bhopal</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-bhopal</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>12.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>18.3 (P2)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Jalandhar</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>courier services in jalandhar</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-jalandhar</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>24.0 (P3)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Kanpur</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Home 14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>courier services in kanpur</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-kanpur</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>14.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>19.5 (P2)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>18.9 (P2)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>18.4 (P2)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Home 18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Home 23</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Home 10</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>courier services in chennai</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-chennai</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>17.8 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23.3 (P3) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10.5 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>36.0 (P4)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Trivandrum</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>tracking 96</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>courier services in trivandrum</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-trivandrum</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>96.0 (P10) – https://www.xpressbees.com/shipment/tracking</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Amritsar</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Home 11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>courier services in amritsar</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-amritsar</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>11.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>20.0 (P2)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Home 21</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>20.7 (P3) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Lucknow</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Broken URL 4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Home 14</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>courier services in lucknow</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-lucknow</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4.0 (P1) – https://www.xpressbees.com/blog/cheap-courier-services-for-businesses/</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14.0 (P2) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>21.9 (P3)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>19.0 (P2)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Varanasi</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Home 26</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>courier services in varanasi</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-varanasi</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>26.5 (P3) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>15.0 (P2)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Surat</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Home 90</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Home 5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>courier services in surat</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-surat</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>89.5 (P9) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5.0 (P1) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>23.2 (P3)</t>
         </is>
@@ -3942,713 +4086,844 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>City page URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>June</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in bangalore</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-bengaluru</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>19.5 (P2)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Home 28</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>28.0 (P3) – https://www.xpressbees.com/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in kolkata</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-kolkata</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1.9 (P1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in delhi</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-delhi</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>12.8 (P2)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>14.5 (P2)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in mumbai</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-mumbai</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1.0 (P1)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>8.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in hyderabad</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-hyderabad</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>4.5 (P1)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2.3 (P1)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gurgaon</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in gurgaon</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-gurgaon</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>4.3 (P1)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in pune</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-pune</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>9.3 (P1)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>8.2 (P1)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Indore</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in indore</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-indore</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>3.8 (P1)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>4.7 (P1)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bhubaneswar</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in bhubaneswar</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-bhubaneswar</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>5.3 (P1)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>3.7 (P1)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chandigarh</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in chandigarh</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-chandigarh</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>5.4 (P1)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>4.4 (P1)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ahmedabad</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in ahmedabad</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-ahmedabad</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>26.1 (P3)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>5.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in noida</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-noida</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>11.9 (P2)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>4.5 (P1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jaipur</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in jaipur</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-jaipur</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>5.0 (P1)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>5.2 (P1)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vadodara</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in vadodara</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-vadodara</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>3.5 (P1)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>3.6 (P1)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Patna</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in patna</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-patna</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>4.8 (P1)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>5.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ludhiana</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in ludhiana</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-ludhiana</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>3.8 (P1)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Bhopal</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in bhopal</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-bhopal</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>5.2 (P1)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>5.5 (P1)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Jalandhar</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in jalandhar</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-jalandhar</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2.9 (P1)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2.2 (P1)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Kanpur</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in kanpur</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-kanpur</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>6.0 (P1)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>transport-services 49</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in chennai</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-chennai</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49.0 (P5) – https://www.xpressbees.com/services/transport-services-from-chennai</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Trivandrum</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in trivandrum</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-trivandrum</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>3.1 (P1)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>3.2 (P1)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Amritsar</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in amritsar</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-amritsar</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>3.4 (P1)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>3.5 (P1)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Lucknow</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in lucknow</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-lucknow</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>4.3 (P1)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Varanasi</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in varanasi</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-varanasi</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>2.9 (P1)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2.6 (P1)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Surat</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ecommerce shipping in surat</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/courier-services-in-surat</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2.3 (P1)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
@@ -4665,794 +4940,940 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>City page URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>June</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>July</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>September</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in kolkata</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-kolkata</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>8.0 (P1)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>8.4 (P1)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in pune</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-pune</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>5.2 (P1)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>3.2 (P1)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in delhi</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-delhi</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>4.9 (P1)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>5.8 (P1)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in mumbai</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-mumbai</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>5.2 (P1)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>courier-services-i 47</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in bengaluru</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-bengaluru</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>47.0 (P5) – https://www.xpressbees.com/services/courier-services-in-bengaluru</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ahmedabad</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in ahmedabad</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-ahmedabad</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>5.1 (P1)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>5.9 (P1)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Surat</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in surat</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-surat</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>7.6 (P1)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Jaipur</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in jaipur</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-jaipur</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>6.7 (P1)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>5.3 (P1)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Faridabad</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in faridabad</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-faridabad</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>4.2 (P1)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2.3 (P1)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Patna</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in patna</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-patna</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>4.8 (P1)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>5.5 (P1)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Gandhinagar</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>transport-services 28</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in gandhinagar</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-gandhinagar</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28.5 (P3) – https://www.xpressbees.com/services/transport-services-from-ahmedabad</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>8.8 (P1)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in hyderabad</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-hyderabad</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>7.6 (P1)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>3.2 (P1)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in chennai</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-chennai</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>6.7 (P1)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>6.6 (P1)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Indore</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in indore</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-indore</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2.4 (P1)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1.7 (P1)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Nagpur</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in nagpur</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-nagpur</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>5.8 (P1)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>6.3 (P1)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Nashik</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in nashik</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-nashik</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>4.4 (P1)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2.8 (P1)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Coimbatore</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in coimbatore</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-coimbatore</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>4.2 (P1)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>4.8 (P1)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Lucknow</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in lucknow</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-lucknow</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>5.9 (P1)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>3.5 (P1)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Chandigarh</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in chandigarh</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-chandigarh</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>3.6 (P1)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Raipur</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Home 25</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in raipur</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-raipur</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>25.0 (P3) – https://www.xpressbees.com/</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Ludhiana</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in ludhiana</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-ludhiana</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>5.0 (P1)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>7.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Rajkot</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in rajkot</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-rajkot</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>5.0 (P1)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>4.8 (P1)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Kochi</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in kochi</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-kochi</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>8.3 (P1)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>5.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Vadodara</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in vadodara</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-vadodara</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>4.0 (P1)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Guwahati</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in guwahati</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-guwahati</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>10.4 (P2)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>11.5 (P2)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tiruppur</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in tiruppur</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-tiruppur</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1.5 (P1)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Kanpur</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in kanpur</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-kanpur</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>4.2 (P1)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>b2b transport services in noida</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xpressbees.com/services/transport-services-from-noida</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>6.6 (P1)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>7.8 (P1)</t>
         </is>
@@ -5469,10 +5890,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="130" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5485,26 +5906,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Format: average position (P = Google results page; P1 = positions 1-10).</t>
+          <t>Position format: average position (P = Google results page; P1 = positions 1-10).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>City sheets: a number with (P#) = the city page itself ranks. 'Home 13' etc. = the city page did not rank; the homepage ranked instead at that position.</t>
+          <t>Keyword sheets: 'Ranking page URL' is the page whose position is shown. Where Google ranked different pages in different months, each month's URL is listed.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>No data = no impressions recorded in Search Console for that keyword that month.</t>
+          <t>City sheets: a plain position means the city page URL ranked. 'position – URL' means the city page did not rank that month and the URL shown ranked instead.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>No data = no impressions recorded in Search Console for that keyword that month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Keywords with very few impressions (1-5 a month) have unstable averages; treat them as indicative only.</t>
         </is>
